--- a/data/LM2_LMI_Summary.xlsx
+++ b/data/LM2_LMI_Summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\Mba rida\Event\MAILER\without raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dafha\Work Colleague\OS\Mba rida\Event\MAILER\new begin_stk\without raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEC8057A-9E74-433C-B5BB-C2D158D3CDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA52CF72-6F8B-418B-A0DF-18D58CFE9605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F673BAF6-C00D-42EA-9313-7CB2BD08351B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{F673BAF6-C00D-42EA-9313-7CB2BD08351B}"/>
   </bookViews>
   <sheets>
     <sheet name="By Store" sheetId="4" r:id="rId1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -804,13 +806,13 @@
         <v>17781.228319000002</v>
       </c>
       <c r="D4" s="5">
-        <v>15202.198791000001</v>
+        <v>15177.183385</v>
       </c>
       <c r="E4" s="5">
-        <v>2579.029528</v>
+        <v>2604.044934</v>
       </c>
       <c r="F4" s="9">
-        <v>14.504225927092996</v>
+        <v>14.644910280002799</v>
       </c>
       <c r="G4" s="5">
         <v>13480.811870000001</v>
@@ -825,13 +827,13 @@
         <v>24.185148358984971</v>
       </c>
       <c r="K4" s="3">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="L4" s="3">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="M4" s="9">
-        <v>88.927335640138409</v>
+        <v>89.0625</v>
       </c>
       <c r="N4" s="3">
         <v>47</v>
@@ -848,13 +850,13 @@
         <v>5851.9620800000002</v>
       </c>
       <c r="D5" s="5">
-        <v>5527.3764959999999</v>
+        <v>5521.9744220000002</v>
       </c>
       <c r="E5" s="5">
-        <v>324.58558399999998</v>
+        <v>329.98765800000001</v>
       </c>
       <c r="F5" s="9">
-        <v>5.5466111974532817</v>
+        <v>5.6389233814037292</v>
       </c>
       <c r="G5" s="5">
         <v>2564.3425180000004</v>
@@ -869,13 +871,13 @@
         <v>56.179782388473711</v>
       </c>
       <c r="K5" s="3">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L5" s="3">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M5" s="9">
-        <v>68.565400843881847</v>
+        <v>69.787234042553195</v>
       </c>
       <c r="N5" s="3">
         <v>43</v>
@@ -892,13 +894,13 @@
         <v>7782.5462280000002</v>
       </c>
       <c r="D6" s="5">
-        <v>7353.18678</v>
+        <v>7344.3367539999999</v>
       </c>
       <c r="E6" s="5">
-        <v>429.35944799999999</v>
+        <v>438.209474</v>
       </c>
       <c r="F6" s="9">
-        <v>5.5169533905915396</v>
+        <v>5.6306697212207037</v>
       </c>
       <c r="G6" s="5">
         <v>2876.1633090000005</v>
@@ -913,13 +915,13 @@
         <v>63.043415037457059</v>
       </c>
       <c r="K6" s="3">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L6" s="3">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M6" s="9">
-        <v>74.451097804391225</v>
+        <v>75.150300601202403</v>
       </c>
       <c r="N6" s="3">
         <v>18</v>
@@ -936,13 +938,13 @@
         <v>10388.199951000001</v>
       </c>
       <c r="D7" s="5">
-        <v>9857.5076339999996</v>
+        <v>9839.6876969999994</v>
       </c>
       <c r="E7" s="5">
-        <v>530.692317</v>
+        <v>548.51225399999998</v>
       </c>
       <c r="F7" s="9">
-        <v>5.108607068628034</v>
+        <v>5.2801472496416331</v>
       </c>
       <c r="G7" s="5">
         <v>7243.9145120000003</v>
@@ -957,13 +959,13 @@
         <v>30.267856354625916</v>
       </c>
       <c r="K7" s="3">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="L7" s="3">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M7" s="9">
-        <v>86.932849364791281</v>
+        <v>87.431693989071036</v>
       </c>
       <c r="N7" s="3">
         <v>31</v>
@@ -980,13 +982,13 @@
         <v>16435.204753999999</v>
       </c>
       <c r="D8" s="5">
-        <v>14999.179199</v>
+        <v>14979.463946</v>
       </c>
       <c r="E8" s="5">
-        <v>1436.0255549999999</v>
+        <v>1455.740808</v>
       </c>
       <c r="F8" s="9">
-        <v>8.7374971988134202</v>
+        <v>8.857454651702481</v>
       </c>
       <c r="G8" s="5">
         <v>11685.599071999997</v>
@@ -1001,13 +1003,13 @@
         <v>28.898974811032041</v>
       </c>
       <c r="K8" s="3">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="L8" s="3">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M8" s="9">
-        <v>84.843205574912901</v>
+        <v>84.965034965034974</v>
       </c>
       <c r="N8" s="3">
         <v>34</v>
@@ -1024,13 +1026,13 @@
         <v>4341.3183419999996</v>
       </c>
       <c r="D9" s="5">
-        <v>3920.6894950000001</v>
+        <v>3839.8671789999999</v>
       </c>
       <c r="E9" s="5">
-        <v>420.62884700000001</v>
+        <v>501.45116300000001</v>
       </c>
       <c r="F9" s="9">
-        <v>9.6889657441297139</v>
+        <v>11.550665569689293</v>
       </c>
       <c r="G9" s="5">
         <v>3664.2313929999996</v>
@@ -1045,13 +1047,13 @@
         <v>15.596344143886789</v>
       </c>
       <c r="K9" s="3">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="L9" s="3">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="M9" s="9">
-        <v>77.868852459016395</v>
+        <v>77.983539094650197</v>
       </c>
       <c r="N9" s="3">
         <v>38</v>
@@ -1068,13 +1070,13 @@
         <v>7675.8348820000001</v>
       </c>
       <c r="D10" s="5">
-        <v>7140.9173609999998</v>
+        <v>7108.7986309999997</v>
       </c>
       <c r="E10" s="5">
-        <v>534.91752099999997</v>
+        <v>567.03625099999999</v>
       </c>
       <c r="F10" s="9">
-        <v>6.9688513265754741</v>
+        <v>7.387290890398285</v>
       </c>
       <c r="G10" s="5">
         <v>3727.8191770000003</v>
@@ -1089,13 +1091,13 @@
         <v>51.434349040756231</v>
       </c>
       <c r="K10" s="3">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="L10" s="3">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M10" s="9">
-        <v>81.488549618320619</v>
+        <v>81.992337164750964</v>
       </c>
       <c r="N10" s="3">
         <v>19</v>
@@ -1112,13 +1114,13 @@
         <v>5084.8640859999996</v>
       </c>
       <c r="D11" s="5">
-        <v>4490.4087719999998</v>
+        <v>4484.0591139999997</v>
       </c>
       <c r="E11" s="5">
-        <v>594.45531400000004</v>
+        <v>600.80497200000002</v>
       </c>
       <c r="F11" s="9">
-        <v>11.690682463602037</v>
+        <v>11.815556165093536</v>
       </c>
       <c r="G11" s="5">
         <v>3665.5462739999994</v>
@@ -1133,13 +1135,13 @@
         <v>27.912600769561653</v>
       </c>
       <c r="K11" s="3">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L11" s="3">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="M11" s="9">
-        <v>67.617107942973519</v>
+        <v>68.507157464212682</v>
       </c>
       <c r="N11" s="3">
         <v>45</v>
@@ -1156,13 +1158,13 @@
         <v>2991.759176</v>
       </c>
       <c r="D12" s="5">
-        <v>2585.630674</v>
+        <v>2578.2256379999999</v>
       </c>
       <c r="E12" s="5">
-        <v>406.12850200000003</v>
+        <v>413.53353800000002</v>
       </c>
       <c r="F12" s="9">
-        <v>13.574906204282</v>
+        <v>13.822420645263863</v>
       </c>
       <c r="G12" s="5">
         <v>2861.5753920000002</v>
@@ -1177,13 +1179,13 @@
         <v>4.3514125416356704</v>
       </c>
       <c r="K12" s="3">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L12" s="3">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M12" s="9">
-        <v>74.304068522483931</v>
+        <v>75.646551724137936</v>
       </c>
       <c r="N12" s="3">
         <v>44</v>
@@ -1200,13 +1202,13 @@
         <v>5493.7182519999997</v>
       </c>
       <c r="D13" s="5">
-        <v>5109.2578320000002</v>
+        <v>5103.5196159999996</v>
       </c>
       <c r="E13" s="5">
-        <v>384.46042</v>
+        <v>390.19863600000002</v>
       </c>
       <c r="F13" s="9">
-        <v>6.9981823305197057</v>
+        <v>7.1026328271921733</v>
       </c>
       <c r="G13" s="5">
         <v>3480.2521179999994</v>
@@ -1221,13 +1223,13 @@
         <v>36.650334830458284</v>
       </c>
       <c r="K13" s="3">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L13" s="3">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="M13" s="9">
-        <v>76.680672268907571</v>
+        <v>76.631578947368411</v>
       </c>
       <c r="N13" s="3">
         <v>33</v>
@@ -1244,13 +1246,13 @@
         <v>3555.5217069999999</v>
       </c>
       <c r="D14" s="5">
-        <v>2794.0882120000001</v>
+        <v>2778.1577699999998</v>
       </c>
       <c r="E14" s="5">
-        <v>761.43349499999999</v>
+        <v>777.36393699999996</v>
       </c>
       <c r="F14" s="9">
-        <v>21.415520920626459</v>
+        <v>21.863568867250908</v>
       </c>
       <c r="G14" s="5">
         <v>3245.9491379999999</v>
@@ -1265,13 +1267,13 @@
         <v>8.7068113911531793</v>
       </c>
       <c r="K14" s="3">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L14" s="3">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="M14" s="9">
-        <v>74.696356275303643</v>
+        <v>75.8130081300813</v>
       </c>
       <c r="N14" s="3">
         <v>46</v>
@@ -1288,13 +1290,13 @@
         <v>6071.0700509999997</v>
       </c>
       <c r="D15" s="5">
-        <v>5215.8127459999996</v>
+        <v>5204.1089069999998</v>
       </c>
       <c r="E15" s="5">
-        <v>855.25730499999997</v>
+        <v>866.96114399999999</v>
       </c>
       <c r="F15" s="9">
-        <v>14.087422774163604</v>
+        <v>14.280203270874761</v>
       </c>
       <c r="G15" s="5">
         <v>6071.0700509999997</v>
@@ -1309,13 +1311,13 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L15" s="3">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="M15" s="9">
-        <v>84.558823529411768</v>
+        <v>85.239852398523979</v>
       </c>
       <c r="N15" s="3">
         <v>45</v>
@@ -1458,13 +1460,13 @@
         <v>93693.693124000012</v>
       </c>
       <c r="D19" s="11">
-        <v>84436.719287999993</v>
+        <v>84199.848355000009</v>
       </c>
       <c r="E19" s="11">
-        <v>9256.9738359999992</v>
+        <v>9493.8447689999994</v>
       </c>
       <c r="F19" s="12">
-        <v>9.8800394427282825</v>
+        <v>10.13285361314049</v>
       </c>
       <c r="G19" s="11">
         <v>64807.740119999995</v>
@@ -1479,13 +1481,13 @@
         <v>30.830200028267164</v>
       </c>
       <c r="K19" s="11">
-        <v>6164</v>
+        <v>6138</v>
       </c>
       <c r="L19" s="11">
-        <v>4858</v>
+        <v>4874</v>
       </c>
       <c r="M19" s="12">
-        <v>78.812459441920836</v>
+        <v>79.406972955360061</v>
       </c>
       <c r="N19" s="11">
         <v>443</v>
@@ -1787,13 +1789,13 @@
         <v>4366.6924799999997</v>
       </c>
       <c r="D8" s="5">
-        <v>3781.7108410000001</v>
+        <v>3763.8375070000002</v>
       </c>
       <c r="E8" s="5">
-        <v>584.98163899999997</v>
+        <v>602.85497299999997</v>
       </c>
       <c r="F8" s="9">
-        <v>13.396446891538375</v>
+        <v>13.805757464285648</v>
       </c>
       <c r="G8" s="16">
         <v>4200.1015779999998</v>
@@ -1808,13 +1810,13 @@
         <v>3.9663541204002755</v>
       </c>
       <c r="K8" s="5">
-        <v>700</v>
+        <v>723</v>
       </c>
       <c r="L8" s="5">
-        <v>558</v>
+        <v>581</v>
       </c>
       <c r="M8" s="9">
-        <v>79.714285714285722</v>
+        <v>80.359612724757952</v>
       </c>
       <c r="N8" s="2">
         <v>56</v>
@@ -1831,13 +1833,13 @@
         <v>14262.497665000001</v>
       </c>
       <c r="D9" s="23">
-        <v>13128.122422999999</v>
+        <v>13110.249088999999</v>
       </c>
       <c r="E9" s="23">
-        <v>1134.3752420000001</v>
+        <v>1152.248576</v>
       </c>
       <c r="F9" s="24">
-        <v>7.9535525168480365</v>
+        <v>8.0788695154538335</v>
       </c>
       <c r="G9" s="23">
         <v>14095.788916</v>
@@ -1852,13 +1854,13 @@
         <v>1.1826847719801654</v>
       </c>
       <c r="K9" s="25">
-        <v>971</v>
+        <v>994</v>
       </c>
       <c r="L9" s="25">
-        <v>805</v>
+        <v>828</v>
       </c>
       <c r="M9" s="24">
-        <v>82.904222451081353</v>
+        <v>83.299798792756548</v>
       </c>
       <c r="N9" s="25">
         <v>84</v>
@@ -2051,13 +2053,13 @@
         <v>17716.457978999999</v>
       </c>
       <c r="D14" s="5">
-        <v>12850.927584999999</v>
+        <v>12676.644673000001</v>
       </c>
       <c r="E14" s="5">
-        <v>4865.5303940000003</v>
+        <v>5039.813306</v>
       </c>
       <c r="F14" s="9">
-        <v>27.463336067329607</v>
+        <v>28.447070582471312</v>
       </c>
       <c r="G14" s="16">
         <v>10777.911080999998</v>
@@ -2072,13 +2074,13 @@
         <v>64.377473945129509</v>
       </c>
       <c r="K14" s="5">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="L14" s="5">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="M14" s="9">
-        <v>81.213017751479285</v>
+        <v>81.54069767441861</v>
       </c>
       <c r="N14" s="2">
         <v>46</v>
@@ -2227,13 +2229,13 @@
         <v>53578.363326999999</v>
       </c>
       <c r="D18" s="26">
-        <v>46303.815495000003</v>
+        <v>46129.532583</v>
       </c>
       <c r="E18" s="26">
-        <v>7274.5478320000002</v>
+        <v>7448.8307440000008</v>
       </c>
       <c r="F18" s="24">
-        <v>13.577398375538102</v>
+        <v>13.902684370065996</v>
       </c>
       <c r="G18" s="26">
         <v>30636.337201999999</v>
@@ -2248,13 +2250,13 @@
         <v>74.885016357315379</v>
       </c>
       <c r="K18" s="25">
-        <v>3057</v>
+        <v>3069</v>
       </c>
       <c r="L18" s="25">
-        <v>2427</v>
+        <v>2439</v>
       </c>
       <c r="M18" s="24">
-        <v>79.391560353287531</v>
+        <v>79.47214076246334</v>
       </c>
       <c r="N18" s="25">
         <v>180</v>
@@ -2271,13 +2273,13 @@
         <v>8112.0713290000003</v>
       </c>
       <c r="D19" s="5">
-        <v>7882.4119950000004</v>
+        <v>7831.9188210000002</v>
       </c>
       <c r="E19" s="5">
-        <v>229.659334</v>
+        <v>280.15250800000001</v>
       </c>
       <c r="F19" s="9">
-        <v>2.8310812946008799</v>
+        <v>3.45352619125127</v>
       </c>
       <c r="G19" s="16">
         <v>5940.1439220000002</v>
@@ -2292,13 +2294,13 @@
         <v>36.563548552351058</v>
       </c>
       <c r="K19" s="5">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="L19" s="5">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="M19" s="9">
-        <v>80.709219858156033</v>
+        <v>81.032078103207809</v>
       </c>
       <c r="N19" s="2">
         <v>25</v>
@@ -2315,13 +2317,13 @@
         <v>7465.7373280000002</v>
       </c>
       <c r="D20" s="5">
-        <v>7182.4981090000001</v>
+        <v>7188.2765959999997</v>
       </c>
       <c r="E20" s="5">
-        <v>283.23921899999999</v>
+        <v>277.46073200000001</v>
       </c>
       <c r="F20" s="9">
-        <v>3.7938545994341468</v>
+        <v>3.7164545149397736</v>
       </c>
       <c r="G20" s="16">
         <v>4411.2435540000006</v>
@@ -2336,13 +2338,13 @@
         <v>69.243371775069292</v>
       </c>
       <c r="K20" s="5">
-        <v>1006</v>
+        <v>933</v>
       </c>
       <c r="L20" s="5">
-        <v>728</v>
+        <v>697</v>
       </c>
       <c r="M20" s="9">
-        <v>72.365805168986086</v>
+        <v>74.705251875669887</v>
       </c>
       <c r="N20" s="2">
         <v>39</v>
@@ -2359,13 +2361,13 @@
         <v>15577.808657000001</v>
       </c>
       <c r="D21" s="26">
-        <v>15064.910104000001</v>
+        <v>15020.195416999999</v>
       </c>
       <c r="E21" s="26">
-        <v>512.89855299999999</v>
+        <v>557.61324000000002</v>
       </c>
       <c r="F21" s="24">
-        <v>3.2924948835440038</v>
+        <v>3.5795358145539455</v>
       </c>
       <c r="G21" s="26">
         <v>10351.387476</v>
@@ -2380,13 +2382,13 @@
         <v>50.490054527642911</v>
       </c>
       <c r="K21" s="25">
-        <v>1711</v>
+        <v>1650</v>
       </c>
       <c r="L21" s="25">
-        <v>1297</v>
+        <v>1278</v>
       </c>
       <c r="M21" s="24">
-        <v>75.803623611922859</v>
+        <v>77.454545454545453</v>
       </c>
       <c r="N21" s="25">
         <v>64</v>
@@ -3019,13 +3021,13 @@
         <v>93693.693123999998</v>
       </c>
       <c r="D36" s="29">
-        <v>84436.719288000008</v>
+        <v>84199.848355000009</v>
       </c>
       <c r="E36" s="29">
-        <v>9256.973836000001</v>
+        <v>9493.8447690000012</v>
       </c>
       <c r="F36" s="30">
-        <v>9.8800394427282878</v>
+        <v>10.132853613140496</v>
       </c>
       <c r="G36" s="29">
         <v>64807.740120000002</v>
@@ -3040,13 +3042,13 @@
         <v>44.571764037002183</v>
       </c>
       <c r="K36" s="31">
-        <v>6164</v>
+        <v>6138</v>
       </c>
       <c r="L36" s="31">
-        <v>4858</v>
+        <v>4874</v>
       </c>
       <c r="M36" s="30">
-        <v>78.812459441920836</v>
+        <v>79.406972955360061</v>
       </c>
       <c r="N36" s="31">
         <v>443</v>
